--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -1818,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117528687</v>
+        <v>117528565</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>90782</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,37 +1830,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Knippen (Knippen), Jmt</t>
@@ -1902,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1903,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,7 +1930,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117528315</v>
+        <v>117528687</v>
       </c>
       <c r="B13" t="n">
         <v>97836</v>
@@ -1972,17 +1963,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Knippen (Knippen), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489748</v>
+        <v>489782</v>
       </c>
       <c r="R13" t="n">
-        <v>6949082</v>
+        <v>6949009</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117528565</v>
+        <v>117528315</v>
       </c>
       <c r="B14" t="n">
-        <v>90782</v>
+        <v>97836</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,25 +2063,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489782</v>
+        <v>489748</v>
       </c>
       <c r="R14" t="n">
-        <v>6949009</v>
+        <v>6949082</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2862,7 +2862,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117868468</v>
+        <v>117868388</v>
       </c>
       <c r="B21" t="n">
         <v>97836</v>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489789</v>
+        <v>489787</v>
       </c>
       <c r="R21" t="n">
-        <v>6948958</v>
+        <v>6948976</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,10 +2974,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117867596</v>
+        <v>117868468</v>
       </c>
       <c r="B22" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2986,25 +2986,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489769</v>
+        <v>489789</v>
       </c>
       <c r="R22" t="n">
-        <v>6948867</v>
+        <v>6948958</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117868388</v>
+        <v>117867596</v>
       </c>
       <c r="B23" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3098,25 +3098,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489787</v>
+        <v>489769</v>
       </c>
       <c r="R23" t="n">
-        <v>6948976</v>
+        <v>6948867</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -1821,7 +1821,7 @@
         <v>117528565</v>
       </c>
       <c r="B12" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>117528687</v>
       </c>
       <c r="B13" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>117528315</v>
       </c>
       <c r="B14" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117794618</v>
+        <v>117794030</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,41 +2175,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gillhov (Gillhov), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490142</v>
+        <v>490123</v>
       </c>
       <c r="R15" t="n">
-        <v>6948834</v>
+        <v>6948863</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2238,7 +2247,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2248,7 +2257,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117794030</v>
+        <v>117797336</v>
       </c>
       <c r="B16" t="n">
-        <v>97836</v>
+        <v>90784</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,50 +2296,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gillhov (Gillhov), Jmt</t>
+          <t>Knippen (Knippen), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490123</v>
+        <v>489741</v>
       </c>
       <c r="R16" t="n">
-        <v>6948863</v>
+        <v>6949100</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117797336</v>
+        <v>117794618</v>
       </c>
       <c r="B17" t="n">
-        <v>90782</v>
+        <v>78482</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,34 +2412,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Knippen (Knippen), Jmt</t>
+          <t>Gillhov (Gillhov), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489741</v>
+        <v>490142</v>
       </c>
       <c r="R17" t="n">
-        <v>6949100</v>
+        <v>6948834</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,7 +2511,7 @@
         <v>117796330</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117849139</v>
+        <v>117848563</v>
       </c>
       <c r="B19" t="n">
-        <v>78480</v>
+        <v>79592</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2650,38 +2650,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Knippen (Knippen), Jmt</t>
+          <t>Gillhov (Gillhov), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489999</v>
+        <v>490143</v>
       </c>
       <c r="R19" t="n">
-        <v>6948890</v>
+        <v>6948822</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117848563</v>
+        <v>117849139</v>
       </c>
       <c r="B20" t="n">
-        <v>79590</v>
+        <v>78482</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2762,38 +2762,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gillhov (Gillhov), Jmt</t>
+          <t>Knippen (Knippen), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490143</v>
+        <v>489999</v>
       </c>
       <c r="R20" t="n">
-        <v>6948822</v>
+        <v>6948890</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>22:14</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>22:14</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2865,7 +2865,7 @@
         <v>117868388</v>
       </c>
       <c r="B21" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2974,10 +2974,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117868468</v>
+        <v>117867596</v>
       </c>
       <c r="B22" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2986,25 +2986,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489789</v>
+        <v>489769</v>
       </c>
       <c r="R22" t="n">
-        <v>6948958</v>
+        <v>6948867</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117867596</v>
+        <v>117868468</v>
       </c>
       <c r="B23" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3098,25 +3098,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489769</v>
+        <v>489789</v>
       </c>
       <c r="R23" t="n">
-        <v>6948867</v>
+        <v>6948958</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3201,7 +3201,7 @@
         <v>118042375</v>
       </c>
       <c r="B24" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -7586,10 +7586,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119936493</v>
+        <v>119937923</v>
       </c>
       <c r="B61" t="n">
-        <v>91228</v>
+        <v>90527</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7598,25 +7598,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>898</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489779</v>
+        <v>489790</v>
       </c>
       <c r="R61" t="n">
-        <v>6948874</v>
+        <v>6948858</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7810,10 +7810,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119937923</v>
+        <v>119936493</v>
       </c>
       <c r="B63" t="n">
-        <v>90527</v>
+        <v>91228</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7822,25 +7822,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>898</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489790</v>
+        <v>489779</v>
       </c>
       <c r="R63" t="n">
-        <v>6948858</v>
+        <v>6948874</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -7586,10 +7586,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119937923</v>
+        <v>119936614</v>
       </c>
       <c r="B61" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7598,25 +7598,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489790</v>
+        <v>489781</v>
       </c>
       <c r="R61" t="n">
-        <v>6948858</v>
+        <v>6948874</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7698,10 +7698,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119936614</v>
+        <v>119936493</v>
       </c>
       <c r="B62" t="n">
-        <v>90562</v>
+        <v>91228</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7710,25 +7710,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7738,7 +7738,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489781</v>
+        <v>489779</v>
       </c>
       <c r="R62" t="n">
         <v>6948874</v>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7810,10 +7810,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119936493</v>
+        <v>119937923</v>
       </c>
       <c r="B63" t="n">
-        <v>91228</v>
+        <v>90527</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7822,25 +7822,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>898</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489779</v>
+        <v>489790</v>
       </c>
       <c r="R63" t="n">
-        <v>6948874</v>
+        <v>6948858</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -7586,10 +7586,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119936614</v>
+        <v>119936493</v>
       </c>
       <c r="B61" t="n">
-        <v>90562</v>
+        <v>91246</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7598,25 +7598,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489781</v>
+        <v>489779</v>
       </c>
       <c r="R61" t="n">
         <v>6948874</v>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7698,10 +7698,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119936493</v>
+        <v>119937923</v>
       </c>
       <c r="B62" t="n">
-        <v>91228</v>
+        <v>90545</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7710,25 +7710,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>898</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7738,10 +7738,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489779</v>
+        <v>489790</v>
       </c>
       <c r="R62" t="n">
-        <v>6948874</v>
+        <v>6948858</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7810,10 +7810,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119937923</v>
+        <v>119936614</v>
       </c>
       <c r="B63" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7822,25 +7822,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489790</v>
+        <v>489781</v>
       </c>
       <c r="R63" t="n">
-        <v>6948858</v>
+        <v>6948874</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -7586,10 +7586,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119936493</v>
+        <v>119937923</v>
       </c>
       <c r="B61" t="n">
-        <v>91246</v>
+        <v>90545</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7598,25 +7598,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>898</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489779</v>
+        <v>489790</v>
       </c>
       <c r="R61" t="n">
-        <v>6948874</v>
+        <v>6948858</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7698,10 +7698,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119937923</v>
+        <v>119936493</v>
       </c>
       <c r="B62" t="n">
-        <v>90545</v>
+        <v>91246</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7710,25 +7710,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>898</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7738,10 +7738,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489790</v>
+        <v>489779</v>
       </c>
       <c r="R62" t="n">
-        <v>6948858</v>
+        <v>6948874</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -7586,10 +7586,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119937923</v>
+        <v>119936614</v>
       </c>
       <c r="B61" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7598,25 +7598,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489790</v>
+        <v>489781</v>
       </c>
       <c r="R61" t="n">
-        <v>6948858</v>
+        <v>6948874</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7810,10 +7810,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119936614</v>
+        <v>119937923</v>
       </c>
       <c r="B63" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7822,25 +7822,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489781</v>
+        <v>489790</v>
       </c>
       <c r="R63" t="n">
-        <v>6948874</v>
+        <v>6948858</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -7586,10 +7586,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119936614</v>
+        <v>119936493</v>
       </c>
       <c r="B61" t="n">
-        <v>90580</v>
+        <v>91246</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7598,25 +7598,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489781</v>
+        <v>489779</v>
       </c>
       <c r="R61" t="n">
         <v>6948874</v>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7698,10 +7698,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119936493</v>
+        <v>119936614</v>
       </c>
       <c r="B62" t="n">
-        <v>91246</v>
+        <v>90580</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7710,25 +7710,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7738,7 +7738,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489779</v>
+        <v>489781</v>
       </c>
       <c r="R62" t="n">
         <v>6948874</v>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -1128,34 +1128,34 @@
         <v>111915405</v>
       </c>
       <c r="B6" t="n">
-        <v>89094</v>
+        <v>90333</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>256335</v>
+        <v>5754</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,14 +1164,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nordvallen (Nordvallen), Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>490124</v>
       </c>
       <c r="R6" t="n">
-        <v>6948875</v>
+        <v>6948876</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -1128,7 +1128,7 @@
         <v>111915405</v>
       </c>
       <c r="B6" t="n">
-        <v>90333</v>
+        <v>90345</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -1128,7 +1128,7 @@
         <v>111915405</v>
       </c>
       <c r="B6" t="n">
-        <v>90345</v>
+        <v>90349</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -1128,7 +1128,7 @@
         <v>111915405</v>
       </c>
       <c r="B6" t="n">
-        <v>90349</v>
+        <v>90354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,11 +1142,6 @@
       </c>
       <c r="E6" t="n">
         <v>5754</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Gultoppig fingersvamp</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -1128,7 +1128,7 @@
         <v>111915405</v>
       </c>
       <c r="B6" t="n">
-        <v>90354</v>
+        <v>90367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,6 +1142,11 @@
       </c>
       <c r="E6" t="n">
         <v>5754</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -1128,7 +1128,7 @@
         <v>111915405</v>
       </c>
       <c r="B6" t="n">
-        <v>90367</v>
+        <v>90380</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -1128,7 +1128,7 @@
         <v>111915405</v>
       </c>
       <c r="B6" t="n">
-        <v>90487</v>
+        <v>90491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111790785</v>
+        <v>119293120</v>
       </c>
       <c r="B2" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åsvarptjärnen (Åsvarptjärnen), Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489818</v>
+        <v>489994</v>
       </c>
       <c r="R2" t="n">
-        <v>6949032</v>
+        <v>6948932</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,27 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:34</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Många träd med mycket lav i området</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,66 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111792337</v>
+        <v>117528565</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsvarptjärnen (Åsvarptjärnen), Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489764</v>
+        <v>489782</v>
       </c>
       <c r="R3" t="n">
-        <v>6949092</v>
+        <v>6949009</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,54 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111790625</v>
+        <v>117797336</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åsvarptjärnen (Åsvarptjärnen), Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489825</v>
+        <v>489741</v>
       </c>
       <c r="R4" t="n">
-        <v>6949021</v>
+        <v>6949100</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,56 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111919588</v>
+        <v>119936493</v>
       </c>
       <c r="B5" t="n">
-        <v>78713</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gillhov, Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490133</v>
+        <v>489779</v>
       </c>
       <c r="R5" t="n">
-        <v>6948774</v>
+        <v>6948874</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,12 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1085,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111915405</v>
+        <v>112213279</v>
       </c>
       <c r="B6" t="n">
-        <v>90491</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,40 +1114,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5754</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490124</v>
+        <v>490080</v>
       </c>
       <c r="R6" t="n">
-        <v>6948876</v>
+        <v>6948906</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,12 +1169,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,34 +1193,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112212902</v>
+        <v>118042375</v>
       </c>
       <c r="B7" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,35 +1222,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kälen (Kälen), Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490134</v>
+        <v>489798</v>
       </c>
       <c r="R7" t="n">
-        <v>6948772</v>
+        <v>6948987</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1302,22 +1276,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,70 +1306,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112212105</v>
+        <v>119316201</v>
       </c>
       <c r="B8" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nordvallen (Nordvallen), Jmt</t>
+          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490018</v>
+        <v>489796</v>
       </c>
       <c r="R8" t="n">
-        <v>6948882</v>
+        <v>6948987</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1419,22 +1383,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,72 +1413,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112212882</v>
+        <v>119936614</v>
       </c>
       <c r="B9" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kälen (Kälen), Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490109</v>
+        <v>489781</v>
       </c>
       <c r="R9" t="n">
-        <v>6948768</v>
+        <v>6948874</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1541,22 +1490,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,72 +1520,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112212836</v>
+        <v>119937923</v>
       </c>
       <c r="B10" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stugunäset (Stugunäset), Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490078</v>
+        <v>489790</v>
       </c>
       <c r="R10" t="n">
-        <v>6948752</v>
+        <v>6948858</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1663,22 +1597,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,27 +1627,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112213279</v>
+        <v>111915405</v>
       </c>
       <c r="B11" t="n">
-        <v>89592</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,38 +1650,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5754</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nordvallen (Nordvallen), Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490080</v>
+        <v>490124</v>
       </c>
       <c r="R11" t="n">
-        <v>6948907</v>
+        <v>6948876</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,22 +1707,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,33 +1721,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117528315</v>
+        <v>111790785</v>
       </c>
       <c r="B12" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,37 +1751,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Knippen (Knippen), Jmt</t>
+          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489748</v>
+        <v>489818</v>
       </c>
       <c r="R12" t="n">
-        <v>6949082</v>
+        <v>6949032</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,22 +1806,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Många träd med mycket lav i området</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,15 +1853,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117528831</v>
+        <v>117794618</v>
       </c>
       <c r="B13" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,37 +1864,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Knippen (Knippen), Jmt</t>
+          <t>Gillhov, Gillhov, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489782</v>
+        <v>490142</v>
       </c>
       <c r="R13" t="n">
-        <v>6949009</v>
+        <v>6948834</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2000,22 +1918,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>22:27</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>22:27</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,53 +1960,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117528565</v>
+        <v>117849139</v>
       </c>
       <c r="B14" t="n">
-        <v>90784</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Knippen (Knippen), Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489782</v>
+        <v>489999</v>
       </c>
       <c r="R14" t="n">
-        <v>6949009</v>
+        <v>6948890</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2112,22 +2025,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,19 +2067,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117794618</v>
+        <v>117867596</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2190,14 +2098,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gillhov (Gillhov), Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490142</v>
+        <v>489769</v>
       </c>
       <c r="R15" t="n">
-        <v>6948834</v>
+        <v>6948867</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2224,22 +2132,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,53 +2174,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117797336</v>
+        <v>119293112</v>
       </c>
       <c r="B16" t="n">
-        <v>90786</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Knippen (Knippen), Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489741</v>
+        <v>489989</v>
       </c>
       <c r="R16" t="n">
-        <v>6949100</v>
+        <v>6948932</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2336,22 +2239,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,27 +2269,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117794030</v>
+        <v>119293175</v>
       </c>
       <c r="B17" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2394,43 +2292,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gillhov (Gillhov), Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490123</v>
+        <v>490008</v>
       </c>
       <c r="R17" t="n">
-        <v>6948863</v>
+        <v>6948930</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,22 +2346,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,27 +2376,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117796330</v>
+        <v>119294430</v>
       </c>
       <c r="B18" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2515,46 +2399,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åsvarptjärnen (Åsvarptjärnen), Jmt</t>
+          <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489818</v>
+        <v>489987</v>
       </c>
       <c r="R18" t="n">
-        <v>6949320</v>
+        <v>6948905</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,27 +2453,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:48</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Alldeles vid en kallkälla, Åsvarpkällan</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,72 +2477,69 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117848563</v>
+        <v>111919588</v>
       </c>
       <c r="B19" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gillhov (Gillhov), Jmt</t>
+          <t>Gillhov, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490143</v>
+        <v>490133</v>
       </c>
       <c r="R19" t="n">
-        <v>6948822</v>
+        <v>6948774</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2699,22 +2563,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>22:14</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>22:14</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2723,6 +2577,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2741,15 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117849139</v>
+        <v>112212902</v>
       </c>
       <c r="B20" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2757,34 +2607,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Knippen (Knippen), Jmt</t>
+          <t>Kälen, Kälen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489999</v>
+        <v>490133</v>
       </c>
       <c r="R20" t="n">
-        <v>6948890</v>
+        <v>6948771</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2811,22 +2662,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2841,62 +2692,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117868388</v>
+        <v>117848563</v>
       </c>
       <c r="B21" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Knippen (Knippen), Jmt</t>
+          <t>Gillhov, Gillhov, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489787</v>
+        <v>490143</v>
       </c>
       <c r="R21" t="n">
-        <v>6948976</v>
+        <v>6948822</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2923,22 +2769,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>22:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>22:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,15 +2811,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117868468</v>
+        <v>111790625</v>
       </c>
       <c r="B22" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,19 +2840,20 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Knippen (Knippen), Jmt</t>
+          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489789</v>
+        <v>489824</v>
       </c>
       <c r="R22" t="n">
-        <v>6948958</v>
+        <v>6949020</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3035,22 +2877,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3077,53 +2919,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117867596</v>
+        <v>111792337</v>
       </c>
       <c r="B23" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Knippen (Knippen), Jmt</t>
+          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489769</v>
+        <v>489763</v>
       </c>
       <c r="R23" t="n">
-        <v>6948867</v>
+        <v>6949091</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3147,22 +2985,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3189,50 +3027,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118042375</v>
+        <v>112212105</v>
       </c>
       <c r="B24" t="n">
-        <v>90504</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Knippen (Knippen), Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489798</v>
+        <v>490018</v>
       </c>
       <c r="R24" t="n">
-        <v>6948987</v>
+        <v>6948882</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3259,22 +3097,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,27 +3127,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119294613</v>
+        <v>112212836</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3336,7 +3169,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3344,19 +3177,20 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489859</v>
+        <v>490078</v>
       </c>
       <c r="R25" t="n">
-        <v>6948941</v>
+        <v>6948752</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3380,22 +3214,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,53 +3256,58 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119294430</v>
+        <v>112212882</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stugunäset, Stugunäset, Jmt</t>
+          <t>Kälen, Kälen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489987</v>
+        <v>490108</v>
       </c>
       <c r="R26" t="n">
-        <v>6948905</v>
+        <v>6948768</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3492,22 +3331,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3522,27 +3361,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119293684</v>
+        <v>117528315</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3570,17 +3404,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stugunäset, Stugunäset, Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489987</v>
+        <v>489748</v>
       </c>
       <c r="R27" t="n">
-        <v>6948905</v>
+        <v>6949082</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3604,22 +3438,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3634,62 +3468,66 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119293112</v>
+        <v>117528687</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nordvallen, Nordvallen, Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489989</v>
+        <v>489782</v>
       </c>
       <c r="R28" t="n">
-        <v>6948932</v>
+        <v>6949009</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3716,22 +3554,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3746,27 +3584,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119295546</v>
+        <v>117794030</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3793,7 +3626,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3803,14 +3636,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stugunäset, Stugunäset, Jmt</t>
+          <t>Gillhov, Gillhov, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489854</v>
+        <v>490123</v>
       </c>
       <c r="R29" t="n">
-        <v>6948983</v>
+        <v>6948863</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3837,22 +3670,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3867,62 +3700,69 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119293630</v>
+        <v>117796330</v>
       </c>
       <c r="B30" t="n">
-        <v>96868</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nordvallen, Nordvallen, Jmt</t>
+          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490035</v>
+        <v>489818</v>
       </c>
       <c r="R30" t="n">
-        <v>6948907</v>
+        <v>6949320</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3949,22 +3789,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Alldeles vid en kallkälla, Åsvarpkällan</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3973,71 +3818,67 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119293978</v>
+        <v>117868388</v>
       </c>
       <c r="B31" t="n">
-        <v>96868</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stugunäset, Stugunäset, Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490082</v>
+        <v>489787</v>
       </c>
       <c r="R31" t="n">
-        <v>6948808</v>
+        <v>6948976</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4061,22 +3902,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4091,65 +3932,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119293120</v>
+        <v>117868468</v>
       </c>
       <c r="B32" t="n">
-        <v>78560</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nordvallen, Nordvallen, Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489994</v>
+        <v>489789</v>
       </c>
       <c r="R32" t="n">
-        <v>6948932</v>
+        <v>6948958</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4173,22 +4009,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4203,27 +4039,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119295272</v>
+        <v>119293684</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4248,29 +4079,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489859</v>
+        <v>489987</v>
       </c>
       <c r="R33" t="n">
-        <v>6948946</v>
+        <v>6948905</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4299,7 +4121,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4309,7 +4131,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4324,27 +4146,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119293876</v>
+        <v>119293210</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4371,7 +4188,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4381,14 +4198,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stugunäset, Stugunäset, Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490055</v>
+        <v>490001</v>
       </c>
       <c r="R34" t="n">
-        <v>6948813</v>
+        <v>6948919</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4457,15 +4274,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119293210</v>
+        <v>119293876</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,7 +4304,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4502,14 +4314,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nordvallen, Nordvallen, Jmt</t>
+          <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490001</v>
+        <v>490055</v>
       </c>
       <c r="R35" t="n">
-        <v>6948919</v>
+        <v>6948813</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4581,12 +4393,7 @@
         <v>119294314</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4699,15 +4506,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119294640</v>
+        <v>119294366</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4734,7 +4536,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4748,10 +4550,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489846</v>
+        <v>489865</v>
       </c>
       <c r="R37" t="n">
-        <v>6948938</v>
+        <v>6948903</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4820,50 +4622,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119293175</v>
+        <v>119294613</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nordvallen, Nordvallen, Jmt</t>
+          <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490008</v>
+        <v>489859</v>
       </c>
       <c r="R38" t="n">
-        <v>6948930</v>
+        <v>6948941</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4932,15 +4738,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119294366</v>
+        <v>119294640</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4967,7 +4768,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4981,10 +4782,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489865</v>
+        <v>489846</v>
       </c>
       <c r="R39" t="n">
-        <v>6948903</v>
+        <v>6948938</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5056,12 +4857,7 @@
         <v>119295049</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5174,15 +4970,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119315246</v>
+        <v>119295272</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5209,7 +5000,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5223,10 +5014,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490066</v>
+        <v>489859</v>
       </c>
       <c r="R41" t="n">
-        <v>6948820</v>
+        <v>6948946</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5253,22 +5044,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5283,27 +5074,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119315971</v>
+        <v>119295546</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5344,10 +5130,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489857</v>
+        <v>489854</v>
       </c>
       <c r="R42" t="n">
-        <v>6948954</v>
+        <v>6948983</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5374,22 +5160,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5404,27 +5190,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119316326</v>
+        <v>119314481</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5454,21 +5235,16 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489811</v>
+        <v>490003</v>
       </c>
       <c r="R43" t="n">
-        <v>6949016</v>
+        <v>6948906</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5500,7 +5276,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5510,7 +5286,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5537,15 +5313,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119316812</v>
+        <v>119314515</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5572,7 +5343,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5580,24 +5351,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489825</v>
+        <v>490007</v>
       </c>
       <c r="R44" t="n">
-        <v>6949032</v>
+        <v>6948905</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5626,7 +5392,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5636,7 +5402,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5666,12 +5432,7 @@
         <v>119314619</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5789,15 +5550,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119314515</v>
+        <v>119314679</v>
       </c>
       <c r="B46" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5824,7 +5580,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5838,13 +5594,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490007</v>
+        <v>490045</v>
       </c>
       <c r="R46" t="n">
-        <v>6948905</v>
+        <v>6948882</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5873,7 +5629,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5883,7 +5639,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5910,50 +5666,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119316187</v>
+        <v>119314882</v>
       </c>
       <c r="B47" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
+          <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489796</v>
+        <v>490067</v>
       </c>
       <c r="R47" t="n">
-        <v>6948987</v>
+        <v>6948797</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5985,7 +5745,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5995,7 +5755,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6022,15 +5782,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119315911</v>
+        <v>119315079</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6057,7 +5812,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6065,16 +5820,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489863</v>
+        <v>490081</v>
       </c>
       <c r="R48" t="n">
-        <v>6948945</v>
+        <v>6948797</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6106,7 +5866,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6116,7 +5876,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6143,15 +5903,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119314679</v>
+        <v>119315246</v>
       </c>
       <c r="B49" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6178,7 +5933,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6188,14 +5943,14 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nordvallen, Nordvallen, Jmt</t>
+          <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490045</v>
+        <v>490066</v>
       </c>
       <c r="R49" t="n">
-        <v>6948882</v>
+        <v>6948820</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6227,7 +5982,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6237,7 +5992,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6264,15 +6019,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119315836</v>
+        <v>119315550</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6313,10 +6063,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489862</v>
+        <v>489865</v>
       </c>
       <c r="R50" t="n">
-        <v>6948926</v>
+        <v>6948925</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6348,7 +6098,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6358,7 +6108,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6385,15 +6135,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119314882</v>
+        <v>119315619</v>
       </c>
       <c r="B51" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6420,7 +6165,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6434,10 +6179,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490067</v>
+        <v>489889</v>
       </c>
       <c r="R51" t="n">
-        <v>6948797</v>
+        <v>6948903</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6469,7 +6214,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6479,7 +6224,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6506,50 +6251,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119316201</v>
+        <v>119315755</v>
       </c>
       <c r="B52" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
+          <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489796</v>
+        <v>489876</v>
       </c>
       <c r="R52" t="n">
-        <v>6948987</v>
+        <v>6948904</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6581,7 +6330,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6591,7 +6340,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6618,15 +6367,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119315943</v>
+        <v>119315836</v>
       </c>
       <c r="B53" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6653,7 +6397,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6667,10 +6411,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489859</v>
+        <v>489862</v>
       </c>
       <c r="R53" t="n">
-        <v>6948958</v>
+        <v>6948926</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6702,7 +6446,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6712,7 +6456,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6739,15 +6483,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119315755</v>
+        <v>119315862</v>
       </c>
       <c r="B54" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6774,7 +6513,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6788,10 +6527,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489876</v>
+        <v>489861</v>
       </c>
       <c r="R54" t="n">
-        <v>6948904</v>
+        <v>6948931</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6823,7 +6562,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6833,7 +6572,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6860,15 +6599,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119314481</v>
+        <v>119315911</v>
       </c>
       <c r="B55" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6895,19 +6629,24 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nordvallen, Nordvallen, Jmt</t>
+          <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490003</v>
+        <v>489863</v>
       </c>
       <c r="R55" t="n">
-        <v>6948906</v>
+        <v>6948945</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6939,7 +6678,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6949,7 +6688,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6976,15 +6715,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119315550</v>
+        <v>119315943</v>
       </c>
       <c r="B56" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7011,7 +6745,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7025,10 +6759,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489865</v>
+        <v>489859</v>
       </c>
       <c r="R56" t="n">
-        <v>6948925</v>
+        <v>6948958</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7060,7 +6794,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7070,7 +6804,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7097,15 +6831,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119316045</v>
+        <v>119315971</v>
       </c>
       <c r="B57" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7146,10 +6875,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489836</v>
+        <v>489857</v>
       </c>
       <c r="R57" t="n">
-        <v>6948982</v>
+        <v>6948954</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7181,7 +6910,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7191,7 +6920,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7218,15 +6947,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119315862</v>
+        <v>119316045</v>
       </c>
       <c r="B58" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7253,7 +6977,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7267,10 +6991,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489861</v>
+        <v>489836</v>
       </c>
       <c r="R58" t="n">
-        <v>6948931</v>
+        <v>6948982</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7302,7 +7026,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7312,7 +7036,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7339,15 +7063,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119315619</v>
+        <v>119316326</v>
       </c>
       <c r="B59" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7374,7 +7093,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7384,14 +7103,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stugunäset, Stugunäset, Jmt</t>
+          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489889</v>
+        <v>489811</v>
       </c>
       <c r="R59" t="n">
-        <v>6948903</v>
+        <v>6949016</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7423,7 +7142,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7433,7 +7152,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7460,15 +7179,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119315079</v>
+        <v>119316775</v>
       </c>
       <c r="B60" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7495,7 +7209,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7510,14 +7224,14 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stugunäset, Stugunäset, Jmt</t>
+          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490081</v>
+        <v>489825</v>
       </c>
       <c r="R60" t="n">
-        <v>6948797</v>
+        <v>6949032</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7549,7 +7263,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7559,7 +7273,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7586,53 +7300,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119936493</v>
+        <v>119293630</v>
       </c>
       <c r="B61" t="n">
-        <v>91246</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>898</v>
+        <v>221941</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Knippen, Knippen, Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489779</v>
+        <v>490035</v>
       </c>
       <c r="R61" t="n">
-        <v>6948874</v>
+        <v>6948907</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7656,22 +7365,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7686,65 +7395,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119936614</v>
+        <v>119293978</v>
       </c>
       <c r="B62" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Knippen, Knippen, Jmt</t>
+          <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489781</v>
+        <v>490082</v>
       </c>
       <c r="R62" t="n">
-        <v>6948874</v>
+        <v>6948808</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7768,22 +7472,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7798,127 +7502,15 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>119937923</v>
-      </c>
-      <c r="B63" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Knippen, Knippen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>489790</v>
-      </c>
-      <c r="R63" t="n">
-        <v>6948858</v>
-      </c>
-      <c r="S63" t="n">
-        <v>20</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Hackås</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>18:34</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>18:34</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3045,49 +3045,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111790625</v>
+        <v>135342355</v>
       </c>
       <c r="B24" t="n">
-        <v>99118</v>
+        <v>57162</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489824</v>
+        <v>489807</v>
       </c>
       <c r="R24" t="n">
-        <v>6949020</v>
+        <v>6949428</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3111,22 +3110,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Tjäderhöna med fem kycklingar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,19 +3145,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111792337</v>
+        <v>111790625</v>
       </c>
       <c r="B25" t="n">
         <v>99118</v>
@@ -3189,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489763</v>
+        <v>489824</v>
       </c>
       <c r="R25" t="n">
-        <v>6949091</v>
+        <v>6949020</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3224,7 +3228,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3234,7 +3238,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3261,7 +3265,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112212105</v>
+        <v>111792337</v>
       </c>
       <c r="B26" t="n">
         <v>99118</v>
@@ -3289,25 +3293,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nordvallen, Nordvallen, Jmt</t>
+          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490018</v>
+        <v>489763</v>
       </c>
       <c r="R26" t="n">
-        <v>6948882</v>
+        <v>6949091</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3331,22 +3331,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3361,19 +3361,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117528315</v>
+        <v>112212105</v>
       </c>
       <c r="B27" t="n">
         <v>99118</v>
@@ -3401,20 +3401,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Knippen, Knippen, Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489748</v>
+        <v>490018</v>
       </c>
       <c r="R27" t="n">
-        <v>6949082</v>
+        <v>6948882</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3438,22 +3443,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,19 +3473,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117528687</v>
+        <v>117528315</v>
       </c>
       <c r="B28" t="n">
         <v>99118</v>
@@ -3508,26 +3513,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489782</v>
+        <v>489748</v>
       </c>
       <c r="R28" t="n">
-        <v>6949009</v>
+        <v>6949082</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3559,7 +3555,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3569,7 +3565,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3596,7 +3592,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117794030</v>
+        <v>117528687</v>
       </c>
       <c r="B29" t="n">
         <v>99118</v>
@@ -3626,7 +3622,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3636,14 +3632,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gillhov, Gillhov, Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490123</v>
+        <v>489782</v>
       </c>
       <c r="R29" t="n">
-        <v>6948863</v>
+        <v>6949009</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3670,22 +3666,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3712,7 +3708,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117796330</v>
+        <v>117794030</v>
       </c>
       <c r="B30" t="n">
         <v>99118</v>
@@ -3742,7 +3738,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3750,19 +3746,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
+          <t>Gillhov, Gillhov, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489818</v>
+        <v>490123</v>
       </c>
       <c r="R30" t="n">
-        <v>6949320</v>
+        <v>6948863</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3794,7 +3787,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3804,12 +3797,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:48</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Alldeles vid en kallkälla, Åsvarpkällan</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3818,7 +3806,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3837,7 +3824,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117868388</v>
+        <v>117796330</v>
       </c>
       <c r="B31" t="n">
         <v>99118</v>
@@ -3865,20 +3852,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Knippen, Knippen, Jmt</t>
+          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489787</v>
+        <v>489818</v>
       </c>
       <c r="R31" t="n">
-        <v>6948976</v>
+        <v>6949320</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3902,22 +3901,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Alldeles vid en kallkälla, Åsvarpkällan</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3926,6 +3930,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3944,7 +3949,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117868468</v>
+        <v>117868388</v>
       </c>
       <c r="B32" t="n">
         <v>99118</v>
@@ -3979,10 +3984,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489789</v>
+        <v>489787</v>
       </c>
       <c r="R32" t="n">
-        <v>6948958</v>
+        <v>6948976</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4014,7 +4019,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4024,7 +4029,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4051,7 +4056,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119293684</v>
+        <v>117868468</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -4082,17 +4087,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stugunäset, Stugunäset, Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489987</v>
+        <v>489789</v>
       </c>
       <c r="R33" t="n">
-        <v>6948905</v>
+        <v>6948958</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4116,22 +4121,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,19 +4151,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119293210</v>
+        <v>119293684</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -4186,29 +4191,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nordvallen, Nordvallen, Jmt</t>
+          <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490001</v>
+        <v>489987</v>
       </c>
       <c r="R34" t="n">
-        <v>6948919</v>
+        <v>6948905</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4237,7 +4233,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4247,7 +4243,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4262,19 +4258,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119293876</v>
+        <v>119293210</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4304,7 +4300,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4314,14 +4310,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stugunäset, Stugunäset, Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490055</v>
+        <v>490001</v>
       </c>
       <c r="R35" t="n">
-        <v>6948813</v>
+        <v>6948919</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4390,7 +4386,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119294314</v>
+        <v>119293876</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4420,7 +4416,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4434,10 +4430,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489866</v>
+        <v>490055</v>
       </c>
       <c r="R36" t="n">
-        <v>6948905</v>
+        <v>6948813</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4506,7 +4502,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119294366</v>
+        <v>119294314</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4536,7 +4532,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4550,10 +4546,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489865</v>
+        <v>489866</v>
       </c>
       <c r="R37" t="n">
-        <v>6948903</v>
+        <v>6948905</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4622,7 +4618,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119294613</v>
+        <v>119294366</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -4652,7 +4648,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4666,10 +4662,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489859</v>
+        <v>489865</v>
       </c>
       <c r="R38" t="n">
-        <v>6948941</v>
+        <v>6948903</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4738,7 +4734,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119294640</v>
+        <v>119294613</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -4768,7 +4764,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4782,10 +4778,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489846</v>
+        <v>489859</v>
       </c>
       <c r="R39" t="n">
-        <v>6948938</v>
+        <v>6948941</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4854,7 +4850,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119295049</v>
+        <v>119294640</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -4884,7 +4880,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4898,10 +4894,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489850</v>
+        <v>489846</v>
       </c>
       <c r="R40" t="n">
-        <v>6948947</v>
+        <v>6948938</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4970,7 +4966,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119295272</v>
+        <v>119295049</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -5000,7 +4996,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5014,10 +5010,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489859</v>
+        <v>489850</v>
       </c>
       <c r="R41" t="n">
-        <v>6948946</v>
+        <v>6948947</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5086,7 +5082,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119295546</v>
+        <v>119295272</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -5116,7 +5112,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5130,10 +5126,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489854</v>
+        <v>489859</v>
       </c>
       <c r="R42" t="n">
-        <v>6948983</v>
+        <v>6948946</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5202,7 +5198,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119314481</v>
+        <v>119295546</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -5235,16 +5231,21 @@
           <t>5</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nordvallen, Nordvallen, Jmt</t>
+          <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490003</v>
+        <v>489854</v>
       </c>
       <c r="R43" t="n">
-        <v>6948906</v>
+        <v>6948983</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5271,22 +5272,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5301,19 +5302,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119314515</v>
+        <v>119314481</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -5343,12 +5344,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5357,13 +5353,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490007</v>
+        <v>490003</v>
       </c>
       <c r="R44" t="n">
-        <v>6948905</v>
+        <v>6948906</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5392,7 +5388,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5402,7 +5398,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5429,7 +5425,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119314619</v>
+        <v>119314515</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -5459,7 +5455,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5467,21 +5463,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490025</v>
+        <v>490007</v>
       </c>
       <c r="R45" t="n">
-        <v>6948884</v>
+        <v>6948905</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5513,7 +5504,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5523,7 +5514,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5550,7 +5541,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119314679</v>
+        <v>119314619</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -5588,19 +5579,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490045</v>
+        <v>490025</v>
       </c>
       <c r="R46" t="n">
-        <v>6948882</v>
+        <v>6948884</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5629,7 +5625,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5639,7 +5635,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5666,7 +5662,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119314882</v>
+        <v>119314679</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -5696,7 +5692,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5706,14 +5702,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stugunäset, Stugunäset, Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490067</v>
+        <v>490045</v>
       </c>
       <c r="R47" t="n">
-        <v>6948797</v>
+        <v>6948882</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5745,7 +5741,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5755,7 +5751,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5782,7 +5778,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119315079</v>
+        <v>119314882</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -5812,7 +5808,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5820,18 +5816,13 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490081</v>
+        <v>490067</v>
       </c>
       <c r="R48" t="n">
         <v>6948797</v>
@@ -5866,7 +5857,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5876,7 +5867,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5903,7 +5894,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119315246</v>
+        <v>119315079</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -5933,7 +5924,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5941,16 +5932,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490066</v>
+        <v>490081</v>
       </c>
       <c r="R49" t="n">
-        <v>6948820</v>
+        <v>6948797</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5982,7 +5978,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5992,7 +5988,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6019,7 +6015,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119315550</v>
+        <v>119315246</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -6049,7 +6045,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6063,10 +6059,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489865</v>
+        <v>490066</v>
       </c>
       <c r="R50" t="n">
-        <v>6948925</v>
+        <v>6948820</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6098,7 +6094,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6108,7 +6104,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6135,7 +6131,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119315619</v>
+        <v>119315550</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -6165,7 +6161,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6179,10 +6175,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489889</v>
+        <v>489865</v>
       </c>
       <c r="R51" t="n">
-        <v>6948903</v>
+        <v>6948925</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6214,7 +6210,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6224,7 +6220,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6251,7 +6247,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119315755</v>
+        <v>119315619</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -6281,7 +6277,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6295,10 +6291,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489876</v>
+        <v>489889</v>
       </c>
       <c r="R52" t="n">
-        <v>6948904</v>
+        <v>6948903</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6330,7 +6326,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6340,7 +6336,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6367,7 +6363,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119315836</v>
+        <v>119315755</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6411,10 +6407,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489862</v>
+        <v>489876</v>
       </c>
       <c r="R53" t="n">
-        <v>6948926</v>
+        <v>6948904</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6446,7 +6442,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6456,7 +6452,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6483,7 +6479,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119315862</v>
+        <v>119315836</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6513,7 +6509,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6527,10 +6523,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489861</v>
+        <v>489862</v>
       </c>
       <c r="R54" t="n">
-        <v>6948931</v>
+        <v>6948926</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6562,7 +6558,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6572,7 +6568,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6599,7 +6595,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119315911</v>
+        <v>119315862</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -6629,7 +6625,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6643,10 +6639,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489863</v>
+        <v>489861</v>
       </c>
       <c r="R55" t="n">
-        <v>6948945</v>
+        <v>6948931</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6678,7 +6674,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6688,7 +6684,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6715,7 +6711,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119315943</v>
+        <v>119315911</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -6745,7 +6741,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6759,10 +6755,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489859</v>
+        <v>489863</v>
       </c>
       <c r="R56" t="n">
-        <v>6948958</v>
+        <v>6948945</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6794,7 +6790,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6804,7 +6800,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6831,7 +6827,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119315971</v>
+        <v>119315943</v>
       </c>
       <c r="B57" t="n">
         <v>99118</v>
@@ -6861,7 +6857,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6875,10 +6871,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489857</v>
+        <v>489859</v>
       </c>
       <c r="R57" t="n">
-        <v>6948954</v>
+        <v>6948958</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6910,7 +6906,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6920,7 +6916,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6947,7 +6943,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119316045</v>
+        <v>119315971</v>
       </c>
       <c r="B58" t="n">
         <v>99118</v>
@@ -6991,10 +6987,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489836</v>
+        <v>489857</v>
       </c>
       <c r="R58" t="n">
-        <v>6948982</v>
+        <v>6948954</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7026,7 +7022,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7036,7 +7032,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7063,7 +7059,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119316326</v>
+        <v>119316045</v>
       </c>
       <c r="B59" t="n">
         <v>99118</v>
@@ -7103,14 +7099,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
+          <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489811</v>
+        <v>489836</v>
       </c>
       <c r="R59" t="n">
-        <v>6949016</v>
+        <v>6948982</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7142,7 +7138,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7152,7 +7148,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7179,7 +7175,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119316775</v>
+        <v>119316326</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -7209,7 +7205,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7217,21 +7213,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489825</v>
+        <v>489811</v>
       </c>
       <c r="R60" t="n">
-        <v>6949032</v>
+        <v>6949016</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7263,7 +7254,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7273,7 +7264,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7300,45 +7291,59 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119293630</v>
+        <v>119316775</v>
       </c>
       <c r="B61" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nordvallen, Nordvallen, Jmt</t>
+          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490035</v>
+        <v>489825</v>
       </c>
       <c r="R61" t="n">
-        <v>6948907</v>
+        <v>6949032</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7365,22 +7370,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7395,19 +7400,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119293978</v>
+        <v>119293630</v>
       </c>
       <c r="B62" t="n">
         <v>97989</v>
@@ -7438,14 +7443,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stugunäset, Stugunäset, Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490082</v>
+        <v>490035</v>
       </c>
       <c r="R62" t="n">
-        <v>6948808</v>
+        <v>6948907</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7511,6 +7516,113 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>119293978</v>
+      </c>
+      <c r="B63" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stugunäset, Stugunäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>490082</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6948808</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212902</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212836</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212882</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119293120</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,6 +1253,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117528565</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,6 +1365,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117797336</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119936493</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1550,6 +1590,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213279</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1657,6 +1702,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118042375</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1764,6 +1814,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119316201</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1871,6 +1926,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119936614</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1978,6 +2038,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119937923</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2079,6 +2144,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111915405</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2192,6 +2262,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111790785</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2299,6 +2374,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117794618</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2406,6 +2486,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117849139</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2513,6 +2598,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117867596</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2620,6 +2710,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119293112</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2727,6 +2822,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119293175</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2834,6 +2934,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119294430</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2935,6 +3040,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111919588</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3042,6 +3152,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117848563</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3154,6 +3269,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135342355</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3262,6 +3382,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111790625</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3370,6 +3495,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111792337</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3482,6 +3612,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212105</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3589,6 +3724,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117528315</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3705,6 +3845,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117528687</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3821,6 +3966,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117794030</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3946,6 +4096,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117796330</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4053,6 +4208,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117868388</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4160,6 +4320,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117868468</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4267,6 +4432,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119293684</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4383,6 +4553,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119293210</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4499,6 +4674,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119293876</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4615,6 +4795,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119294314</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4731,6 +4916,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119294366</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4847,6 +5037,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119294613</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4963,6 +5158,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119294640</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5079,6 +5279,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119295049</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5195,6 +5400,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119295272</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5311,6 +5521,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119295546</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5422,6 +5637,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119314481</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5538,6 +5758,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119314515</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5659,6 +5884,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119314619</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5775,6 +6005,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119314679</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5891,6 +6126,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119314882</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6012,6 +6252,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315079</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6128,6 +6373,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315246</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6244,6 +6494,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315550</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6360,6 +6615,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315619</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6476,6 +6736,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315755</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6592,6 +6857,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315836</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6708,6 +6978,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315862</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6824,6 +7099,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315911</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6940,6 +7220,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315943</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7056,6 +7341,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315971</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7172,6 +7462,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119316045</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7288,6 +7583,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119316326</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7409,6 +7709,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119316775</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7516,6 +7821,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119293630</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7623,8 +7933,77 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119293978</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -3163,7 +3163,7 @@
         <v>135342355</v>
       </c>
       <c r="B24" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 4716-2023 artfynd.xlsx
+++ b/artfynd/A 4716-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3160,49 +3160,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111790625</v>
+        <v>135342355</v>
       </c>
       <c r="B24" t="n">
-        <v>99118</v>
+        <v>57167</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489824</v>
+        <v>489807</v>
       </c>
       <c r="R24" t="n">
-        <v>6949020</v>
+        <v>6949428</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3226,22 +3225,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Tjäderhöna med fem kycklingar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,24 +3260,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111790625</t>
+          <t>https://artportalen.se/Sighting/135342355</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111792337</v>
+        <v>111790625</v>
       </c>
       <c r="B25" t="n">
         <v>99118</v>
@@ -3309,10 +3313,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489763</v>
+        <v>489824</v>
       </c>
       <c r="R25" t="n">
-        <v>6949091</v>
+        <v>6949020</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3344,7 +3348,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3354,7 +3358,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3380,13 +3384,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111792337</t>
+          <t>https://artportalen.se/Sighting/111790625</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112212105</v>
+        <v>111792337</v>
       </c>
       <c r="B26" t="n">
         <v>99118</v>
@@ -3414,25 +3418,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nordvallen, Nordvallen, Jmt</t>
+          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490018</v>
+        <v>489763</v>
       </c>
       <c r="R26" t="n">
-        <v>6948882</v>
+        <v>6949091</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3456,22 +3456,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3486,24 +3486,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112212105</t>
+          <t>https://artportalen.se/Sighting/111792337</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117528315</v>
+        <v>112212105</v>
       </c>
       <c r="B27" t="n">
         <v>99118</v>
@@ -3531,20 +3531,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Knippen, Knippen, Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489748</v>
+        <v>490018</v>
       </c>
       <c r="R27" t="n">
-        <v>6949082</v>
+        <v>6948882</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3568,22 +3573,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3598,24 +3603,24 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117528315</t>
+          <t>https://artportalen.se/Sighting/112212105</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117528687</v>
+        <v>117528315</v>
       </c>
       <c r="B28" t="n">
         <v>99118</v>
@@ -3643,26 +3648,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489782</v>
+        <v>489748</v>
       </c>
       <c r="R28" t="n">
-        <v>6949009</v>
+        <v>6949082</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3694,7 +3690,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3704,7 +3700,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3730,13 +3726,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117528687</t>
+          <t>https://artportalen.se/Sighting/117528315</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117794030</v>
+        <v>117528687</v>
       </c>
       <c r="B29" t="n">
         <v>99118</v>
@@ -3766,7 +3762,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3776,14 +3772,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gillhov, Gillhov, Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490123</v>
+        <v>489782</v>
       </c>
       <c r="R29" t="n">
-        <v>6948863</v>
+        <v>6949009</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3810,22 +3806,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3851,13 +3847,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117794030</t>
+          <t>https://artportalen.se/Sighting/117528687</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117796330</v>
+        <v>117794030</v>
       </c>
       <c r="B30" t="n">
         <v>99118</v>
@@ -3887,7 +3883,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3895,19 +3891,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
+          <t>Gillhov, Gillhov, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489818</v>
+        <v>490123</v>
       </c>
       <c r="R30" t="n">
-        <v>6949320</v>
+        <v>6948863</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3939,7 +3932,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3949,12 +3942,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:48</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Alldeles vid en kallkälla, Åsvarpkällan</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3963,7 +3951,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3981,13 +3968,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117796330</t>
+          <t>https://artportalen.se/Sighting/117794030</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117868388</v>
+        <v>117796330</v>
       </c>
       <c r="B31" t="n">
         <v>99118</v>
@@ -4015,20 +4002,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Knippen, Knippen, Jmt</t>
+          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489787</v>
+        <v>489818</v>
       </c>
       <c r="R31" t="n">
-        <v>6948976</v>
+        <v>6949320</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4052,22 +4051,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Alldeles vid en kallkälla, Åsvarpkällan</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4076,6 +4080,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4093,13 +4098,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117868388</t>
+          <t>https://artportalen.se/Sighting/117796330</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117868468</v>
+        <v>117868388</v>
       </c>
       <c r="B32" t="n">
         <v>99118</v>
@@ -4134,10 +4139,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489789</v>
+        <v>489787</v>
       </c>
       <c r="R32" t="n">
-        <v>6948958</v>
+        <v>6948976</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4169,7 +4174,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4179,7 +4184,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4205,13 +4210,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117868468</t>
+          <t>https://artportalen.se/Sighting/117868388</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119293684</v>
+        <v>117868468</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -4242,17 +4247,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stugunäset, Stugunäset, Jmt</t>
+          <t>Knippen, Knippen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489987</v>
+        <v>489789</v>
       </c>
       <c r="R33" t="n">
-        <v>6948905</v>
+        <v>6948958</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4276,22 +4281,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4306,24 +4311,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119293684</t>
+          <t>https://artportalen.se/Sighting/117868468</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119293210</v>
+        <v>119293684</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -4351,29 +4356,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nordvallen, Nordvallen, Jmt</t>
+          <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490001</v>
+        <v>489987</v>
       </c>
       <c r="R34" t="n">
-        <v>6948919</v>
+        <v>6948905</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4402,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4412,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4427,24 +4423,24 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119293210</t>
+          <t>https://artportalen.se/Sighting/119293684</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119293876</v>
+        <v>119293210</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4474,7 +4470,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4484,14 +4480,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stugunäset, Stugunäset, Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490055</v>
+        <v>490001</v>
       </c>
       <c r="R35" t="n">
-        <v>6948813</v>
+        <v>6948919</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4559,13 +4555,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119293876</t>
+          <t>https://artportalen.se/Sighting/119293210</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119294314</v>
+        <v>119293876</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4595,7 +4591,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4609,10 +4605,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489866</v>
+        <v>490055</v>
       </c>
       <c r="R36" t="n">
-        <v>6948905</v>
+        <v>6948813</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4680,13 +4676,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119294314</t>
+          <t>https://artportalen.se/Sighting/119293876</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119294366</v>
+        <v>119294314</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4716,7 +4712,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4730,10 +4726,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489865</v>
+        <v>489866</v>
       </c>
       <c r="R37" t="n">
-        <v>6948903</v>
+        <v>6948905</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4801,13 +4797,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119294366</t>
+          <t>https://artportalen.se/Sighting/119294314</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119294613</v>
+        <v>119294366</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -4837,7 +4833,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4851,10 +4847,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489859</v>
+        <v>489865</v>
       </c>
       <c r="R38" t="n">
-        <v>6948941</v>
+        <v>6948903</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4922,13 +4918,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119294613</t>
+          <t>https://artportalen.se/Sighting/119294366</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119294640</v>
+        <v>119294613</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -4958,7 +4954,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4972,10 +4968,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489846</v>
+        <v>489859</v>
       </c>
       <c r="R39" t="n">
-        <v>6948938</v>
+        <v>6948941</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5043,13 +5039,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119294640</t>
+          <t>https://artportalen.se/Sighting/119294613</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119295049</v>
+        <v>119294640</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -5079,7 +5075,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5093,10 +5089,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489850</v>
+        <v>489846</v>
       </c>
       <c r="R40" t="n">
-        <v>6948947</v>
+        <v>6948938</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5164,13 +5160,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119295049</t>
+          <t>https://artportalen.se/Sighting/119294640</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119295272</v>
+        <v>119295049</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -5200,7 +5196,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5214,10 +5210,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489859</v>
+        <v>489850</v>
       </c>
       <c r="R41" t="n">
-        <v>6948946</v>
+        <v>6948947</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5285,13 +5281,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119295272</t>
+          <t>https://artportalen.se/Sighting/119295049</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119295546</v>
+        <v>119295272</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -5321,7 +5317,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5335,10 +5331,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489854</v>
+        <v>489859</v>
       </c>
       <c r="R42" t="n">
-        <v>6948983</v>
+        <v>6948946</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5406,13 +5402,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119295546</t>
+          <t>https://artportalen.se/Sighting/119295272</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119314481</v>
+        <v>119295546</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -5445,16 +5441,21 @@
           <t>5</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nordvallen, Nordvallen, Jmt</t>
+          <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490003</v>
+        <v>489854</v>
       </c>
       <c r="R43" t="n">
-        <v>6948906</v>
+        <v>6948983</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5481,22 +5482,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5511,24 +5512,24 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119314481</t>
+          <t>https://artportalen.se/Sighting/119295546</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119314515</v>
+        <v>119314481</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -5558,12 +5559,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5572,13 +5568,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490007</v>
+        <v>490003</v>
       </c>
       <c r="R44" t="n">
-        <v>6948905</v>
+        <v>6948906</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5607,7 +5603,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5617,7 +5613,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5643,13 +5639,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119314515</t>
+          <t>https://artportalen.se/Sighting/119314481</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119314619</v>
+        <v>119314515</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -5679,7 +5675,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5687,21 +5683,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490025</v>
+        <v>490007</v>
       </c>
       <c r="R45" t="n">
-        <v>6948884</v>
+        <v>6948905</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5733,7 +5724,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5743,7 +5734,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5769,13 +5760,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119314619</t>
+          <t>https://artportalen.se/Sighting/119314515</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119314679</v>
+        <v>119314619</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -5813,19 +5804,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490045</v>
+        <v>490025</v>
       </c>
       <c r="R46" t="n">
-        <v>6948882</v>
+        <v>6948884</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5854,7 +5850,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5864,7 +5860,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5890,13 +5886,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119314679</t>
+          <t>https://artportalen.se/Sighting/119314619</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119314882</v>
+        <v>119314679</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -5926,7 +5922,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5936,14 +5932,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stugunäset, Stugunäset, Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490067</v>
+        <v>490045</v>
       </c>
       <c r="R47" t="n">
-        <v>6948797</v>
+        <v>6948882</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5975,7 +5971,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5985,7 +5981,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6011,13 +6007,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119314882</t>
+          <t>https://artportalen.se/Sighting/119314679</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119315079</v>
+        <v>119314882</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -6047,7 +6043,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6055,18 +6051,13 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490081</v>
+        <v>490067</v>
       </c>
       <c r="R48" t="n">
         <v>6948797</v>
@@ -6101,7 +6092,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6111,7 +6102,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6137,13 +6128,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119315079</t>
+          <t>https://artportalen.se/Sighting/119314882</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119315246</v>
+        <v>119315079</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -6173,7 +6164,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6181,16 +6172,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490066</v>
+        <v>490081</v>
       </c>
       <c r="R49" t="n">
-        <v>6948820</v>
+        <v>6948797</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6222,7 +6218,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6232,7 +6228,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6258,13 +6254,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119315246</t>
+          <t>https://artportalen.se/Sighting/119315079</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119315550</v>
+        <v>119315246</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -6294,7 +6290,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6308,10 +6304,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489865</v>
+        <v>490066</v>
       </c>
       <c r="R50" t="n">
-        <v>6948925</v>
+        <v>6948820</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6343,7 +6339,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6353,7 +6349,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6379,13 +6375,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119315550</t>
+          <t>https://artportalen.se/Sighting/119315246</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119315619</v>
+        <v>119315550</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -6415,7 +6411,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6429,10 +6425,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489889</v>
+        <v>489865</v>
       </c>
       <c r="R51" t="n">
-        <v>6948903</v>
+        <v>6948925</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6464,7 +6460,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6474,7 +6470,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6500,13 +6496,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119315619</t>
+          <t>https://artportalen.se/Sighting/119315550</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119315755</v>
+        <v>119315619</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -6536,7 +6532,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6550,10 +6546,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489876</v>
+        <v>489889</v>
       </c>
       <c r="R52" t="n">
-        <v>6948904</v>
+        <v>6948903</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6585,7 +6581,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6595,7 +6591,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6621,13 +6617,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119315755</t>
+          <t>https://artportalen.se/Sighting/119315619</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119315836</v>
+        <v>119315755</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6671,10 +6667,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489862</v>
+        <v>489876</v>
       </c>
       <c r="R53" t="n">
-        <v>6948926</v>
+        <v>6948904</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6706,7 +6702,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6716,7 +6712,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6742,13 +6738,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119315836</t>
+          <t>https://artportalen.se/Sighting/119315755</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119315862</v>
+        <v>119315836</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6778,7 +6774,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6792,10 +6788,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489861</v>
+        <v>489862</v>
       </c>
       <c r="R54" t="n">
-        <v>6948931</v>
+        <v>6948926</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6827,7 +6823,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6837,7 +6833,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6863,13 +6859,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119315862</t>
+          <t>https://artportalen.se/Sighting/119315836</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119315911</v>
+        <v>119315862</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -6899,7 +6895,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6913,10 +6909,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489863</v>
+        <v>489861</v>
       </c>
       <c r="R55" t="n">
-        <v>6948945</v>
+        <v>6948931</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6948,7 +6944,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6958,7 +6954,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6984,13 +6980,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119315911</t>
+          <t>https://artportalen.se/Sighting/119315862</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119315943</v>
+        <v>119315911</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -7020,7 +7016,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7034,10 +7030,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489859</v>
+        <v>489863</v>
       </c>
       <c r="R56" t="n">
-        <v>6948958</v>
+        <v>6948945</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7069,7 +7065,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7079,7 +7075,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7105,13 +7101,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119315943</t>
+          <t>https://artportalen.se/Sighting/119315911</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119315971</v>
+        <v>119315943</v>
       </c>
       <c r="B57" t="n">
         <v>99118</v>
@@ -7141,7 +7137,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7155,10 +7151,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489857</v>
+        <v>489859</v>
       </c>
       <c r="R57" t="n">
-        <v>6948954</v>
+        <v>6948958</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7190,7 +7186,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7200,7 +7196,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7226,13 +7222,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119315971</t>
+          <t>https://artportalen.se/Sighting/119315943</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119316045</v>
+        <v>119315971</v>
       </c>
       <c r="B58" t="n">
         <v>99118</v>
@@ -7276,10 +7272,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489836</v>
+        <v>489857</v>
       </c>
       <c r="R58" t="n">
-        <v>6948982</v>
+        <v>6948954</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7311,7 +7307,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7321,7 +7317,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7347,13 +7343,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119316045</t>
+          <t>https://artportalen.se/Sighting/119315971</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119316326</v>
+        <v>119316045</v>
       </c>
       <c r="B59" t="n">
         <v>99118</v>
@@ -7393,14 +7389,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
+          <t>Stugunäset, Stugunäset, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489811</v>
+        <v>489836</v>
       </c>
       <c r="R59" t="n">
-        <v>6949016</v>
+        <v>6948982</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7432,7 +7428,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7442,7 +7438,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7468,13 +7464,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119316326</t>
+          <t>https://artportalen.se/Sighting/119316045</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119316775</v>
+        <v>119316326</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -7504,7 +7500,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7512,21 +7508,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489825</v>
+        <v>489811</v>
       </c>
       <c r="R60" t="n">
-        <v>6949032</v>
+        <v>6949016</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7558,7 +7549,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7568,7 +7559,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7594,51 +7585,65 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119316775</t>
+          <t>https://artportalen.se/Sighting/119316326</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119293630</v>
+        <v>119316775</v>
       </c>
       <c r="B61" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nordvallen, Nordvallen, Jmt</t>
+          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490035</v>
+        <v>489825</v>
       </c>
       <c r="R61" t="n">
-        <v>6948907</v>
+        <v>6949032</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7665,22 +7670,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7695,24 +7700,24 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119293630</t>
+          <t>https://artportalen.se/Sighting/119316775</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119293978</v>
+        <v>119293630</v>
       </c>
       <c r="B62" t="n">
         <v>97989</v>
@@ -7743,14 +7748,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stugunäset, Stugunäset, Jmt</t>
+          <t>Nordvallen, Nordvallen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490082</v>
+        <v>490035</v>
       </c>
       <c r="R62" t="n">
-        <v>6948808</v>
+        <v>6948907</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7817,6 +7822,118 @@
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119293630</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>119293978</v>
+      </c>
+      <c r="B63" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stugunäset, Stugunäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>490082</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6948808</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119293978</t>
         </is>
@@ -7885,6 +8002,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
